--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/02-ice-cream-production-checklists.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/02-ice-cream-production-checklists.xlsx
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>▸ Pasteurizing: mix, heat treatment, cooling and aging. Note: pasteurizing your own mix usually requires a STATE frozen dessert or dairy manufacturer license (Vermont, Georgia, Arizona…), and some states also require one to batch-freeze pasteurized mix or run a soft serve machine (Vermont, Massachusetts); with bought pasteurized mix a health permit is usually enough. Check with your state department of agriculture.</t>
+          <t>▸ Pasteurizing: mix, heat treatment, cooling and aging. Note: pasteurizing your own mix usually requires a STATE frozen dessert or dairy manufacturer license (e.g. Vermont, Georgia; Arizona exempts on-premises sales with an approved plan), and some states also require one to batch-freeze pasteurized mix or run a soft serve machine (Vermont, Massachusetts); with bought pasteurized mix a health permit is usually enough. Check with your state department of agriculture or health.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pasteurize at 185 °F for 15 seconds (high-temp); your pasteurizer's validated program and your state license minimums take precedence — log reading: ____ °F</t>
+          <t>Add fats and emulsifiers (cream, butter, egg yolks, stabilizer blend) while the mix HEATS through 104–122 °F, before the pasteurizing hold: anything added after pasteurizing goes in raw — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Add fats and emulsifiers when the mix cools to 104–122 °F — log reading: ____ °F</t>
+          <t>Pasteurize at 185 °F for 15 seconds (the kit's high-temp target); typical state minimums: batch 155 °F for 30 min or HTST 175 °F for 25 s — check your state rules and your pasteurizer's validated program, and keep the recording chart if your license requires one — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Cool the mix fast to 41 °F or below: 135 → 70 °F within 2 h, then to 41 °F within 4 h (pasteurizer cooling cycle or blast freezer) — log reading: ____ °F</t>
+          <t>Cool the mix fast to 41 °F or below: 135 → 70 °F within 2 h, then to 41 °F within 4 h (pasteurizer cooling cycle, a blast chiller or an ice bath; faster if your license says so) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Pasteurizer</t>
         </is>
       </c>
       <c r="D15" s="11" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Clean the batch freezer per the manufacturer: remove dasher, gasket and cylinder, then sanitize</t>
+          <t>Clean the batch freezer per the manufacturer: remove the dasher, scraper blades and door gasket, clean the cylinder in place, then sanitize</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
